--- a/artfynd/A 11756-2026 artfynd.xlsx
+++ b/artfynd/A 11756-2026 artfynd.xlsx
@@ -675,42 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131694622</v>
+        <v>131694377</v>
       </c>
       <c r="B2" t="n">
-        <v>99033</v>
+        <v>58057</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575286</v>
+        <v>575366</v>
       </c>
       <c r="R2" t="n">
-        <v>6410869</v>
+        <v>6410831</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +766,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,46 +784,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131694377</v>
+        <v>131694753</v>
       </c>
       <c r="B3" t="n">
-        <v>58057</v>
+        <v>99033</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575366</v>
+        <v>575284</v>
       </c>
       <c r="R3" t="n">
-        <v>6410831</v>
+        <v>6410886</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,6 +871,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -890,7 +890,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131694753</v>
+        <v>131694622</v>
       </c>
       <c r="B4" t="n">
         <v>99033</v>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575284</v>
+        <v>575286</v>
       </c>
       <c r="R4" t="n">
-        <v>6410886</v>
+        <v>6410869</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1102,7 +1102,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131694954</v>
+        <v>131694940</v>
       </c>
       <c r="B6" t="n">
         <v>99033</v>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575453</v>
+        <v>575407</v>
       </c>
       <c r="R6" t="n">
-        <v>6410987</v>
+        <v>6410979</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1208,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131694940</v>
+        <v>131694954</v>
       </c>
       <c r="B7" t="n">
         <v>99033</v>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575407</v>
+        <v>575453</v>
       </c>
       <c r="R7" t="n">
-        <v>6410979</v>
+        <v>6410987</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 11756-2026 artfynd.xlsx
+++ b/artfynd/A 11756-2026 artfynd.xlsx
@@ -1102,7 +1102,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131694940</v>
+        <v>131694954</v>
       </c>
       <c r="B6" t="n">
         <v>99033</v>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575407</v>
+        <v>575453</v>
       </c>
       <c r="R6" t="n">
-        <v>6410979</v>
+        <v>6410987</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1208,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131694954</v>
+        <v>131694940</v>
       </c>
       <c r="B7" t="n">
         <v>99033</v>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575453</v>
+        <v>575407</v>
       </c>
       <c r="R7" t="n">
-        <v>6410987</v>
+        <v>6410979</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1737,42 +1737,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131694784</v>
+        <v>131694893</v>
       </c>
       <c r="B12" t="n">
-        <v>57895</v>
+        <v>99033</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575261</v>
+        <v>575372</v>
       </c>
       <c r="R12" t="n">
-        <v>6410922</v>
+        <v>6410835</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1818,17 +1818,13 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1847,42 +1843,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131694893</v>
+        <v>131694784</v>
       </c>
       <c r="B13" t="n">
-        <v>99033</v>
+        <v>57895</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1890,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575372</v>
+        <v>575261</v>
       </c>
       <c r="R13" t="n">
-        <v>6410835</v>
+        <v>6410922</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1928,13 +1924,17 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11756-2026 artfynd.xlsx
+++ b/artfynd/A 11756-2026 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>131694753</v>
       </c>
       <c r="B3" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>131694622</v>
       </c>
       <c r="B4" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>131694986</v>
       </c>
       <c r="B5" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>131694954</v>
       </c>
       <c r="B6" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>131694940</v>
       </c>
       <c r="B7" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>131694345</v>
       </c>
       <c r="B8" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>131694581</v>
       </c>
       <c r="B10" t="n">
-        <v>96623</v>
+        <v>96624</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>131694439</v>
       </c>
       <c r="B11" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1737,42 +1737,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131694893</v>
+        <v>131694784</v>
       </c>
       <c r="B12" t="n">
-        <v>99033</v>
+        <v>57895</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575372</v>
+        <v>575261</v>
       </c>
       <c r="R12" t="n">
-        <v>6410835</v>
+        <v>6410922</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1818,13 +1818,17 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1843,42 +1847,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131694784</v>
+        <v>131694893</v>
       </c>
       <c r="B13" t="n">
-        <v>57895</v>
+        <v>99034</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1886,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575261</v>
+        <v>575372</v>
       </c>
       <c r="R13" t="n">
-        <v>6410922</v>
+        <v>6410835</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1924,17 +1928,13 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11756-2026 artfynd.xlsx
+++ b/artfynd/A 11756-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131694377</v>
       </c>
       <c r="B2" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>131694753</v>
       </c>
       <c r="B3" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>131694622</v>
       </c>
       <c r="B4" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>131694986</v>
       </c>
       <c r="B5" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,10 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131694954</v>
+        <v>131694940</v>
       </c>
       <c r="B6" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575453</v>
+        <v>575407</v>
       </c>
       <c r="R6" t="n">
-        <v>6410987</v>
+        <v>6410979</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131694940</v>
+        <v>131694954</v>
       </c>
       <c r="B7" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575407</v>
+        <v>575453</v>
       </c>
       <c r="R7" t="n">
-        <v>6410979</v>
+        <v>6410987</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1317,7 @@
         <v>131694345</v>
       </c>
       <c r="B8" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>131694507</v>
       </c>
       <c r="B9" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>131694581</v>
       </c>
       <c r="B10" t="n">
-        <v>96624</v>
+        <v>96625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>131694439</v>
       </c>
       <c r="B11" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>131694784</v>
       </c>
       <c r="B12" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>131694893</v>
       </c>
       <c r="B13" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>131694554</v>
       </c>
       <c r="B14" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 11756-2026 artfynd.xlsx
+++ b/artfynd/A 11756-2026 artfynd.xlsx
@@ -675,46 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131694377</v>
+        <v>131694753</v>
       </c>
       <c r="B2" t="n">
-        <v>58058</v>
+        <v>99038</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575366</v>
+        <v>575284</v>
       </c>
       <c r="R2" t="n">
-        <v>6410831</v>
+        <v>6410886</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -766,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -784,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131694753</v>
+        <v>131694622</v>
       </c>
       <c r="B3" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575284</v>
+        <v>575286</v>
       </c>
       <c r="R3" t="n">
-        <v>6410886</v>
+        <v>6410869</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,42 +887,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131694622</v>
+        <v>131694377</v>
       </c>
       <c r="B4" t="n">
-        <v>99035</v>
+        <v>58061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -933,13 +934,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575286</v>
+        <v>575366</v>
       </c>
       <c r="R4" t="n">
-        <v>6410869</v>
+        <v>6410831</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,7 +978,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -999,7 +999,7 @@
         <v>131694986</v>
       </c>
       <c r="B5" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,10 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131694940</v>
+        <v>131694954</v>
       </c>
       <c r="B6" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575407</v>
+        <v>575453</v>
       </c>
       <c r="R6" t="n">
-        <v>6410979</v>
+        <v>6410987</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131694954</v>
+        <v>131694940</v>
       </c>
       <c r="B7" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575453</v>
+        <v>575407</v>
       </c>
       <c r="R7" t="n">
-        <v>6410987</v>
+        <v>6410979</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1317,7 @@
         <v>131694345</v>
       </c>
       <c r="B8" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>131694507</v>
       </c>
       <c r="B9" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>131694581</v>
       </c>
       <c r="B10" t="n">
-        <v>96625</v>
+        <v>96628</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>131694439</v>
       </c>
       <c r="B11" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1737,42 +1737,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131694784</v>
+        <v>131694893</v>
       </c>
       <c r="B12" t="n">
-        <v>57896</v>
+        <v>99038</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575261</v>
+        <v>575372</v>
       </c>
       <c r="R12" t="n">
-        <v>6410922</v>
+        <v>6410835</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1818,17 +1818,13 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1847,42 +1843,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131694893</v>
+        <v>131694784</v>
       </c>
       <c r="B13" t="n">
-        <v>99035</v>
+        <v>57899</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1890,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575372</v>
+        <v>575261</v>
       </c>
       <c r="R13" t="n">
-        <v>6410835</v>
+        <v>6410922</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1928,13 +1924,17 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1956,7 +1956,7 @@
         <v>131694554</v>
       </c>
       <c r="B14" t="n">
-        <v>58058</v>
+        <v>58061</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 11756-2026 artfynd.xlsx
+++ b/artfynd/A 11756-2026 artfynd.xlsx
@@ -675,42 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131694753</v>
+        <v>131694377</v>
       </c>
       <c r="B2" t="n">
-        <v>99038</v>
+        <v>58061</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575284</v>
+        <v>575366</v>
       </c>
       <c r="R2" t="n">
-        <v>6410886</v>
+        <v>6410831</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +766,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,7 +784,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131694622</v>
+        <v>131694753</v>
       </c>
       <c r="B3" t="n">
         <v>99038</v>
@@ -824,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575286</v>
+        <v>575284</v>
       </c>
       <c r="R3" t="n">
-        <v>6410869</v>
+        <v>6410886</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,46 +890,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131694377</v>
+        <v>131694622</v>
       </c>
       <c r="B4" t="n">
-        <v>58061</v>
+        <v>99038</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -934,13 +933,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575366</v>
+        <v>575286</v>
       </c>
       <c r="R4" t="n">
-        <v>6410831</v>
+        <v>6410869</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,6 +977,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1737,42 +1737,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131694893</v>
+        <v>131694784</v>
       </c>
       <c r="B12" t="n">
-        <v>99038</v>
+        <v>57899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575372</v>
+        <v>575261</v>
       </c>
       <c r="R12" t="n">
-        <v>6410835</v>
+        <v>6410922</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1818,13 +1818,17 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1843,42 +1847,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131694784</v>
+        <v>131694893</v>
       </c>
       <c r="B13" t="n">
-        <v>57899</v>
+        <v>99038</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1886,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575261</v>
+        <v>575372</v>
       </c>
       <c r="R13" t="n">
-        <v>6410922</v>
+        <v>6410835</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1924,17 +1928,13 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11756-2026 artfynd.xlsx
+++ b/artfynd/A 11756-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131694377</v>
       </c>
       <c r="B2" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>131694753</v>
       </c>
       <c r="B3" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>131694622</v>
       </c>
       <c r="B4" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>131694986</v>
       </c>
       <c r="B5" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>131694954</v>
       </c>
       <c r="B6" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>131694940</v>
       </c>
       <c r="B7" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>131694345</v>
       </c>
       <c r="B8" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>131694507</v>
       </c>
       <c r="B9" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>131694581</v>
       </c>
       <c r="B10" t="n">
-        <v>96628</v>
+        <v>96634</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>131694439</v>
       </c>
       <c r="B11" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1737,42 +1737,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131694784</v>
+        <v>131694893</v>
       </c>
       <c r="B12" t="n">
-        <v>57899</v>
+        <v>99044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575261</v>
+        <v>575372</v>
       </c>
       <c r="R12" t="n">
-        <v>6410922</v>
+        <v>6410835</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1818,17 +1818,13 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1847,42 +1843,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131694893</v>
+        <v>131694784</v>
       </c>
       <c r="B13" t="n">
-        <v>99038</v>
+        <v>57901</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1890,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575372</v>
+        <v>575261</v>
       </c>
       <c r="R13" t="n">
-        <v>6410835</v>
+        <v>6410922</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1928,13 +1924,17 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1956,7 +1956,7 @@
         <v>131694554</v>
       </c>
       <c r="B14" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 11756-2026 artfynd.xlsx
+++ b/artfynd/A 11756-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131694753</v>
       </c>
       <c r="B2" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131694622</v>
       </c>
       <c r="B3" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>131694377</v>
       </c>
       <c r="B4" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>131694986</v>
       </c>
       <c r="B5" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>131694954</v>
       </c>
       <c r="B6" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>131694940</v>
       </c>
       <c r="B7" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>131694345</v>
       </c>
       <c r="B8" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>131694581</v>
       </c>
       <c r="B10" t="n">
-        <v>96685</v>
+        <v>96688</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>131694439</v>
       </c>
       <c r="B11" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>131694893</v>
       </c>
       <c r="B13" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>131694554</v>
       </c>
       <c r="B14" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>132023887</v>
       </c>
       <c r="B15" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>132023743</v>
       </c>
       <c r="B18" t="n">
-        <v>111151</v>
+        <v>111154</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 11756-2026 artfynd.xlsx
+++ b/artfynd/A 11756-2026 artfynd.xlsx
@@ -2065,7 +2065,7 @@
         <v>132023887</v>
       </c>
       <c r="B15" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>132023787</v>
       </c>
       <c r="B16" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>132023830</v>
       </c>
       <c r="B17" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>132023743</v>
       </c>
       <c r="B18" t="n">
-        <v>111154</v>
+        <v>111162</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 11756-2026 artfynd.xlsx
+++ b/artfynd/A 11756-2026 artfynd.xlsx
@@ -2065,7 +2065,7 @@
         <v>132023887</v>
       </c>
       <c r="B15" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>132023787</v>
       </c>
       <c r="B16" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>132023830</v>
       </c>
       <c r="B17" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>132023743</v>
       </c>
       <c r="B18" t="n">
-        <v>111162</v>
+        <v>111173</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 11756-2026 artfynd.xlsx
+++ b/artfynd/A 11756-2026 artfynd.xlsx
@@ -2391,7 +2391,7 @@
         <v>132023743</v>
       </c>
       <c r="B18" t="n">
-        <v>111173</v>
+        <v>111175</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 11756-2026 artfynd.xlsx
+++ b/artfynd/A 11756-2026 artfynd.xlsx
@@ -2391,7 +2391,7 @@
         <v>132023743</v>
       </c>
       <c r="B18" t="n">
-        <v>111175</v>
+        <v>111176</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 11756-2026 artfynd.xlsx
+++ b/artfynd/A 11756-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,40 +675,36 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131694753</v>
+        <v>131694581</v>
       </c>
       <c r="B2" t="n">
-        <v>99098</v>
+        <v>96783</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575284</v>
+        <v>575282</v>
       </c>
       <c r="R2" t="n">
-        <v>6410886</v>
+        <v>6410867</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,42 +777,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131694622</v>
+        <v>132023887</v>
       </c>
       <c r="B3" t="n">
-        <v>99098</v>
+        <v>79992</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575286</v>
+        <v>575349</v>
       </c>
       <c r="R3" t="n">
-        <v>6410869</v>
+        <v>6410779</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,12 +845,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gammal torr tallåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,32 +883,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131694377</v>
+        <v>131694507</v>
       </c>
       <c r="B4" t="n">
-        <v>58109</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -924,7 +920,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -934,13 +930,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575366</v>
+        <v>575330</v>
       </c>
       <c r="R4" t="n">
-        <v>6410831</v>
+        <v>6410861</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,42 +992,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131694986</v>
+        <v>131694784</v>
       </c>
       <c r="B5" t="n">
-        <v>99098</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1039,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575403</v>
+        <v>575261</v>
       </c>
       <c r="R5" t="n">
-        <v>6411051</v>
+        <v>6410922</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,13 +1073,17 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1102,42 +1102,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131694954</v>
+        <v>132023787</v>
       </c>
       <c r="B6" t="n">
-        <v>99098</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575453</v>
+        <v>575602</v>
       </c>
       <c r="R6" t="n">
-        <v>6410987</v>
+        <v>6410868</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,12 +1175,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1189,7 +1194,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1208,42 +1212,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131694940</v>
+        <v>132023830</v>
       </c>
       <c r="B7" t="n">
-        <v>99098</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1251,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575407</v>
+        <v>575339</v>
       </c>
       <c r="R7" t="n">
-        <v>6410979</v>
+        <v>6411131</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,12 +1285,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,7 +1304,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1314,42 +1322,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131694345</v>
+        <v>132023856</v>
       </c>
       <c r="B8" t="n">
-        <v>99098</v>
+        <v>57972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1357,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575355</v>
+        <v>575228</v>
       </c>
       <c r="R8" t="n">
-        <v>6410850</v>
+        <v>6410830</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,12 +1395,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1401,7 +1414,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1420,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131694507</v>
+        <v>131694377</v>
       </c>
       <c r="B9" t="n">
-        <v>57945</v>
+        <v>58136</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1431,21 +1443,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1457,7 +1469,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1467,13 +1479,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575330</v>
+        <v>575366</v>
       </c>
       <c r="R9" t="n">
-        <v>6410861</v>
+        <v>6410831</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,38 +1541,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131694581</v>
+        <v>131694554</v>
       </c>
       <c r="B10" t="n">
-        <v>96688</v>
+        <v>58136</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1568,13 +1588,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575282</v>
+        <v>575283</v>
       </c>
       <c r="R10" t="n">
-        <v>6410867</v>
+        <v>6410851</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1612,7 +1632,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1631,40 +1650,36 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131694439</v>
+        <v>132023743</v>
       </c>
       <c r="B11" t="n">
-        <v>99098</v>
+        <v>111257</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>219677</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1674,13 +1689,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575317</v>
+        <v>575597</v>
       </c>
       <c r="R11" t="n">
-        <v>6410866</v>
+        <v>6410871</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1704,12 +1719,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>3 tallar med mycket murgröna</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1737,42 +1757,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131694784</v>
+        <v>131694345</v>
       </c>
       <c r="B12" t="n">
-        <v>57945</v>
+        <v>99195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1780,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575261</v>
+        <v>575355</v>
       </c>
       <c r="R12" t="n">
-        <v>6410922</v>
+        <v>6410850</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1818,17 +1838,13 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1847,10 +1863,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131694893</v>
+        <v>131694439</v>
       </c>
       <c r="B13" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575372</v>
+        <v>575317</v>
       </c>
       <c r="R13" t="n">
-        <v>6410835</v>
+        <v>6410866</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1953,46 +1969,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131694554</v>
+        <v>131694622</v>
       </c>
       <c r="B14" t="n">
-        <v>58109</v>
+        <v>99195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2000,13 +2012,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575283</v>
+        <v>575286</v>
       </c>
       <c r="R14" t="n">
-        <v>6410851</v>
+        <v>6410869</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2044,6 +2056,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2062,37 +2075,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132023887</v>
+        <v>131694753</v>
       </c>
       <c r="B15" t="n">
-        <v>79946</v>
+        <v>99195</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2100,10 +2118,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575349</v>
+        <v>575284</v>
       </c>
       <c r="R15" t="n">
-        <v>6410779</v>
+        <v>6410886</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,17 +2148,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På gammal torr tallåga</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,42 +2181,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132023787</v>
+        <v>131694893</v>
       </c>
       <c r="B16" t="n">
-        <v>57950</v>
+        <v>99195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2211,10 +2224,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575602</v>
+        <v>575372</v>
       </c>
       <c r="R16" t="n">
-        <v>6410868</v>
+        <v>6410835</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2241,17 +2254,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Födosök</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,6 +2268,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2278,42 +2287,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132023830</v>
+        <v>131694940</v>
       </c>
       <c r="B17" t="n">
-        <v>57950</v>
+        <v>99195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2321,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575339</v>
+        <v>575407</v>
       </c>
       <c r="R17" t="n">
-        <v>6411131</v>
+        <v>6410979</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2351,17 +2360,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Födosök</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2370,6 +2374,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2388,36 +2393,40 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132023743</v>
+        <v>131694954</v>
       </c>
       <c r="B18" t="n">
-        <v>111176</v>
+        <v>99195</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219677</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2427,13 +2436,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575597</v>
+        <v>575453</v>
       </c>
       <c r="R18" t="n">
-        <v>6410871</v>
+        <v>6410987</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2457,17 +2466,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>3 tallar med mycket murgröna</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2492,6 +2496,112 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131694986</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>A 11756, Hallingeberg, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>575403</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6411051</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
